--- a/data/prospects_pme.xlsx
+++ b/data/prospects_pme.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Prospects" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S89"/>
+  <dimension ref="A1:S92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3151,83 +3151,79 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A-témoignage équicoaching</t>
+          <t>B-profil LinkedIn à qualifier</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Armelle Chapalain</t>
+          <t>Samuel Usureau</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Présidente / dirigeante</t>
+          <t>Directeur Commercial</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pôle des Entrepreneurs (95) / FRS Consulting / ARZHELYS</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>L'Isle-Adam (95)</t>
-        </is>
-      </c>
+          <t>JDA Dijon</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/armelle-chapalain-6165564</t>
+          <t>https://fr.linkedin.com/in/samuel-usureau-88b293139</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Affinité cheval : a organisé une journée découverte équicoaching pour des chefs d'entreprise</t>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Journée découverte équicoaching pour entrepreneurs du Val d'Oise</t>
+          <t>Profil remonté sur requête « directeur » + dressage/saut d'obstacles amateur</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.visionsforleaders.com/temoignages-equicoaching-chez-visions-for-leaders/</t>
+          <t>https://fr.linkedin.com/in/samuel-usureau-88b293139</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incertain</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>affinite_cheval</t>
+          <t>cavalier_pratiquant</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>equicoaching</t>
+          <t>dressage</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3244,83 +3240,83 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B-profil LinkedIn à qualifier</t>
+          <t>A-témoignage équicoaching</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Camille Novellon-Cresp</t>
+          <t>Armelle Chapalain</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cadre (maison de champagne familiale)</t>
+          <t>Présidente / dirigeante</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Champagne Launois Père et Fils</t>
+          <t>Pôle des Entrepreneurs (95) / FRS Consulting / ARZHELYS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Champagne</t>
+          <t>L'Isle-Adam (95)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/camille-novellon-cresp-1035a01a2</t>
+          <t>https://fr.linkedin.com/in/armelle-chapalain-6165564</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passionnée d'équitation » + direction</t>
+          <t>Affinité cheval : a organisé une journée découverte équicoaching pour des chefs d'entreprise</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Requête Google « passionnée d'équitation » + directeur/fondateur</t>
+          <t>Journée découverte équicoaching pour entrepreneurs du Val d'Oise</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/camille-novellon-cresp-1035a01a2</t>
+          <t>https://www.visionsforleaders.com/temoignages-equicoaching-chez-visions-for-leaders/</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>incertain</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>cavalier_pratiquant</t>
+          <t>affinite_cheval</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>passionnee d'equitation</t>
+          <t>equicoaching</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3337,7 +3333,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3347,48 +3343,48 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alexandre Boudot</t>
+          <t>Camille Novellon-Cresp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cadre bancaire</t>
+          <t>Cadre (maison de champagne familiale)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caisse d'Epargne Normandie</t>
+          <t>Champagne Launois Père et Fils</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Normandie</t>
+          <t>Champagne</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/boudot-alexandre-9538ba170</t>
+          <t>https://fr.linkedin.com/in/camille-novellon-cresp-1035a01a2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passionné d'équitation » + direction</t>
+          <t>Profil remonté sur requête « passionnée d'équitation » + direction</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Requête Google « passionné d'équitation » + directeur</t>
+          <t>Requête Google « passionnée d'équitation » + directeur/fondateur</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/boudot-alexandre-9538ba170</t>
+          <t>https://fr.linkedin.com/in/camille-novellon-cresp-1035a01a2</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3403,7 +3399,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>passionne d'equitation</t>
+          <t>passionnee d'equitation</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3430,7 +3426,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3440,44 +3436,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Céline Goergen</t>
+          <t>Alexandre Boudot</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cadre (services judiciaires)</t>
+          <t>Cadre bancaire</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Direction des services judiciaires</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>Caisse d'Epargne Normandie</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Normandie</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/c%C3%A9line-goergen-3b82642b5</t>
+          <t>https://fr.linkedin.com/in/boudot-alexandre-9538ba170</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passionnée d'équitation » (secteur public)</t>
+          <t>Profil remonté sur requête « passionné d'équitation » + direction</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Requête Google « passionnée d'équitation »; cible secondaire (secteur public)</t>
+          <t>Requête Google « passionné d'équitation » + directeur</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/c%C3%A9line-goergen-3b82642b5</t>
+          <t>https://fr.linkedin.com/in/boudot-alexandre-9538ba170</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>passionnee d'equitation</t>
+          <t>passionne d'equitation</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3519,7 +3519,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3529,39 +3529,39 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Antoine Cabieu</t>
+          <t>Céline Goergen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cadre / entrepreneur</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Caen (14)</t>
-        </is>
-      </c>
+          <t>Cadre (services judiciaires)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Direction des services judiciaires</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/antoinecabieu</t>
+          <t>https://fr.linkedin.com/in/c%C3%A9line-goergen-3b82642b5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Impliqué dans le Jumping de Cabourg (snippet)</t>
+          <t>Profil remonté sur requête « passionnée d'équitation » (secteur public)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Requête Google « directeur général » + jumping; implication Jumping de Cabourg</t>
+          <t>Requête Google « passionnée d'équitation »; cible secondaire (secteur public)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/antoinecabieu</t>
+          <t>https://fr.linkedin.com/in/c%C3%A9line-goergen-3b82642b5</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>jumping</t>
+          <t>passionnee d'equitation</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3618,69 +3618,69 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Émilien Claude</t>
+          <t>Antoine Cabieu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Dirigeant</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Emilien Claude SAS</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>Cadre / entrepreneur</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Caen (14)</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/emilien-claude-5649b032a</t>
+          <t>https://fr.linkedin.com/in/antoinecabieu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Investit dans des chevaux de sport (snippet)</t>
+          <t>Impliqué dans le Jumping de Cabourg (snippet)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Requêtes Google DG/président + cavalier; investissements dans chevaux de sport mentionnés</t>
+          <t>Requête Google « directeur général » + jumping; implication Jumping de Cabourg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/emilien-claude-5649b032a</t>
+          <t>https://fr.linkedin.com/in/antoinecabieu</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incertain</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>affinite_cheval</t>
+          <t>cavalier_pratiquant</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>mention équestre générique</t>
+          <t>jumping</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3697,7 +3697,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3707,44 +3707,44 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thibault Larhant</t>
+          <t>Émilien Claude</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Directeur d'Enseigne GMS</t>
+          <t>Dirigeant</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grande distribution</t>
+          <t>Emilien Claude SAS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/thibault-larhant-434b19105</t>
+          <t>https://fr.linkedin.com/in/emilien-claude-5649b032a</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Parle de sa passion équitation et du parallèle cheval/management sur son profil</t>
+          <t>Investit dans des chevaux de sport (snippet)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Snippet Google : partage sa passion pour l'équitation et le parallèle avec les relations professionnelles</t>
+          <t>Requêtes Google DG/président + cavalier; investissements dans chevaux de sport mentionnés</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/thibault-larhant-434b19105</t>
+          <t>https://fr.linkedin.com/in/emilien-claude-5649b032a</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3786,7 +3786,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3796,44 +3796,44 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Karine Aignan</t>
+          <t>Thibault Larhant</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DRH &amp; coach professionnelle (HEC)</t>
+          <t>Directeur d'Enseigne GMS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Indépendante</t>
+          <t>Grande distribution</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/karine-aignan-drh-coach</t>
+          <t>https://fr.linkedin.com/in/thibault-larhant-434b19105</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « équitation » + DRH</t>
+          <t>Parle de sa passion équitation et du parallèle cheval/management sur son profil</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Requête Google équitation + DRH; indice à confirmer</t>
+          <t>Snippet Google : partage sa passion pour l'équitation et le parallèle avec les relations professionnelles</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/karine-aignan-drh-coach</t>
+          <t>https://fr.linkedin.com/in/thibault-larhant-434b19105</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>65</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3875,7 +3875,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3885,44 +3885,44 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Katy Wehbe</t>
+          <t>Karine Aignan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Dirigeante</t>
+          <t>DRH &amp; coach professionnelle (HEC)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LC EDL</t>
+          <t>Indépendante</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/katy-wehbe-dirigeante-lc-edl-81a252b0</t>
+          <t>https://fr.linkedin.com/in/karine-aignan-drh-coach</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Profil remonté 2x sur requêtes « cavalière »/« équitation » + dirigeante</t>
+          <t>Profil remonté sur requête « équitation » + DRH</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Requêtes Google « cavalière » et « équitation » + dirigeante</t>
+          <t>Requête Google équitation + DRH; indice à confirmer</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/katy-wehbe-dirigeante-lc-edl-81a252b0</t>
+          <t>https://fr.linkedin.com/in/karine-aignan-drh-coach</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3964,7 +3964,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Heïdi Drillaud</t>
+          <t>Katy Wehbe</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3984,34 +3984,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Société des nouveaux patrimoines / Neoproprio</t>
+          <t>LC EDL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/he%C3%AFdi-drillaud-80a884133</t>
+          <t>https://fr.linkedin.com/in/katy-wehbe-dirigeante-lc-edl-81a252b0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « équitation » + directrice générale</t>
+          <t>Profil remonté 2x sur requêtes « cavalière »/« équitation » + dirigeante</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Requête Google « équitation »/« cavalier » + directrice générale</t>
+          <t>Requêtes Google « cavalière » et « équitation » + dirigeante</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/he%C3%AFdi-drillaud-80a884133</t>
+          <t>https://fr.linkedin.com/in/katy-wehbe-dirigeante-lc-edl-81a252b0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4053,7 +4053,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4063,40 +4063,44 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Laure Le Baron</t>
+          <t>Heïdi Drillaud</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Directrice des ressources humaines</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>Dirigeante</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Société des nouveaux patrimoines / Neoproprio</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/laure-le-baron-drh</t>
+          <t>https://fr.linkedin.com/in/he%C3%AFdi-drillaud-80a884133</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « équitation » + DRH</t>
+          <t>Profil remonté sur requête « équitation » + directrice générale</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Requête Google équitation + DRH; indice à confirmer</t>
+          <t>Requête Google « équitation »/« cavalier » + directrice générale</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/laure-le-baron-drh</t>
+          <t>https://fr.linkedin.com/in/he%C3%AFdi-drillaud-80a884133</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4121,7 +4125,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4138,7 +4142,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>229</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4148,40 +4152,44 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Betty Rafik</t>
+          <t>Marie Dauxerre</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Directrice des ressources humaines</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>Gérante fondatrice</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Abeille Informatique (PME)</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/betty-rafik</t>
+          <t>https://fr.linkedin.com/in/marie-dauxerre-4298b858</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « équitation » + DRH</t>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Requête Google équitation + DRH; indice à confirmer</t>
+          <t>Profil « gérante fondatrice » remonté sur requête équitation/cheval + PME</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/betty-rafik</t>
+          <t>https://fr.linkedin.com/in/marie-dauxerre-4298b858</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4206,7 +4214,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4223,7 +4231,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4233,40 +4241,44 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Isabelle Dumas</t>
+          <t>Joëlle Daumas-Guirado</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Directrice des Ressources Humaines</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>CEO (créatrice de crampons pneus)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>UGIGRIP (PME industrielle)</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/isadms</t>
+          <t>https://fr.linkedin.com/in/jo%C3%ABlle-daumas-guirado/en</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « équitation » + DRH</t>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Requête Google équitation + DRH; indice à confirmer</t>
+          <t>Profil CEO PME remonté sur requête « cavalier/équitation » + indépendant</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/isadms</t>
+          <t>https://fr.linkedin.com/in/jo%C3%ABlle-daumas-guirado/en</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4291,7 +4303,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4308,7 +4320,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4318,23 +4330,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Isabelle Lecomte</t>
+          <t>Laure Le Baron</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DRH à temps partagé / transition</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Indépendante</t>
-        </is>
-      </c>
+          <t>Directrice des ressources humaines</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/isabellelecomte-drh</t>
+          <t>https://fr.linkedin.com/in/laure-le-baron-drh</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -4350,7 +4358,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/isabellelecomte-drh</t>
+          <t>https://fr.linkedin.com/in/laure-le-baron-drh</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4397,7 +4405,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4407,7 +4415,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marion Mathieu</t>
+          <t>Betty Rafik</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4419,7 +4427,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/marion-mathieu-6b525393</t>
+          <t>https://fr.linkedin.com/in/betty-rafik</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -4435,7 +4443,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/marion-mathieu-6b525393</t>
+          <t>https://fr.linkedin.com/in/betty-rafik</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4482,7 +4490,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4492,19 +4500,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Franslie Kongo</t>
+          <t>Isabelle Dumas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Directrice des ressources humaines</t>
+          <t>Directrice des Ressources Humaines</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/franslie-kongo-8a631913a</t>
+          <t>https://fr.linkedin.com/in/isadms</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -4520,7 +4528,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/franslie-kongo-8a631913a</t>
+          <t>https://fr.linkedin.com/in/isadms</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4567,7 +4575,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4577,19 +4585,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Angélique Sylvestre</t>
+          <t>Isabelle Lecomte</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Directrice des ressources humaines</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>DRH à temps partagé / transition</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Indépendante</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/ang%C3%A9lique-sylvestre-41ab49106</t>
+          <t>https://fr.linkedin.com/in/isabellelecomte-drh</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -4605,7 +4617,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/ang%C3%A9lique-sylvestre-41ab49106</t>
+          <t>https://fr.linkedin.com/in/isabellelecomte-drh</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4652,7 +4664,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4662,35 +4674,35 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Caroline Joly</t>
+          <t>Marion Mathieu</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Responsable RH</t>
+          <t>Directrice des ressources humaines</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/caroline-joly-9aa1b56b</t>
+          <t>https://fr.linkedin.com/in/marion-mathieu-6b525393</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « responsable RH » + « équitation » + compétition</t>
+          <t>Profil remonté sur requête « équitation » + DRH</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Requête Google responsable RH + équitation + compétition</t>
+          <t>Requête Google équitation + DRH; indice à confirmer</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/caroline-joly-9aa1b56b</t>
+          <t>https://fr.linkedin.com/in/marion-mathieu-6b525393</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4737,79 +4749,75 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B-à qualifier (association)</t>
+          <t>B-profil LinkedIn à qualifier</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nicolas de Chambure</t>
+          <t>Franslie Kongo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Éleveur (Haras d'Etreham), membre du CA de France Galop</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Haras d'Etreham</t>
-        </is>
-      </c>
+          <t>Directrice des ressources humaines</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Nicolas%20de%20Chambure</t>
+          <t>https://fr.linkedin.com/in/franslie-kongo-8a631913a</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Éleveur-dirigeant du Haras d'Etreham, membre du CA France Galop</t>
+          <t>Profil remonté sur requête « équitation » + DRH</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Présentation des nouvelles instances de France Galop</t>
+          <t>Requête Google équitation + DRH; indice à confirmer</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.lecheval.fr/article/presentation-des-nouvelles-instances-de-france-galop/30208</t>
+          <t>https://fr.linkedin.com/in/franslie-kongo-8a631913a</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>incertain</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>proprietaire_chevaux</t>
+          <t>affinite_cheval</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>haras</t>
+          <t>mention équestre générique</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4826,7 +4834,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4836,43 +4844,35 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nicolas Darribere</t>
+          <t>Angélique Sylvestre</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cadre / dirigeant (jardinerie)</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Jardi Béarn</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Béarn (64)</t>
-        </is>
-      </c>
+          <t>Directrice des ressources humaines</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/nicolas-darribere-733553178</t>
+          <t>https://fr.linkedin.com/in/ang%C3%A9lique-sylvestre-41ab49106</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Profil remonté 2x sur requêtes « équitation »/« cheval » + dirigeant</t>
+          <t>Profil remonté sur requête « équitation » + DRH</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Requêtes Google dirigeante/président + équitation/cheval</t>
+          <t>Requête Google équitation + DRH; indice à confirmer</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/nicolas-darribere-733553178</t>
+          <t>https://fr.linkedin.com/in/ang%C3%A9lique-sylvestre-41ab49106</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4919,83 +4919,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B-à qualifier (presse)</t>
+          <t>B-profil LinkedIn à qualifier</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morgane Suquart</t>
+          <t>Caroline Joly</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fondatrice</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>MMProcess</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Saint-Pierre-Quiberon (56)</t>
-        </is>
-      </c>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Morgane%20Suquart%20MMProcess</t>
+          <t>https://fr.linkedin.com/in/caroline-joly-9aa1b56b</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Contenu la montrant à cheval (snippet presse/LinkedIn)</t>
+          <t>Profil remonté sur requête « responsable RH » + « équitation » + compétition</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Fondatrice de la PME MMProcess, contenu la présentant à cheval</t>
+          <t>Requête Google responsable RH + équitation + compétition</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Morgane%20Suquart%20MMProcess</t>
+          <t>https://fr.linkedin.com/in/caroline-joly-9aa1b56b</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>incertain</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>affinite_cheval</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>mention équestre générique</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5012,75 +5004,79 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B-profil LinkedIn à qualifier</t>
+          <t>B-à qualifier (association)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Julie André</t>
+          <t>Nicolas de Chambure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Front Office Manager (hôtellerie)</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>Éleveur (Haras d'Etreham), membre du CA de France Galop</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Haras d'Etreham</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/julie-andre-b90a35157</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Nicolas%20de%20Chambure</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Galop 7 d'équitation affiché sur le profil (diplôme 2010)</t>
+          <t>Éleveur-dirigeant du Haras d'Etreham, membre du CA France Galop</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Profil LinkedIn mentionnant le Galop 7 (requête site:linkedin "galop 7" + manager)</t>
+          <t>Présentation des nouvelles instances de France Galop</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/julie-andre-b90a35157</t>
+          <t>https://www.lecheval.fr/article/presentation-des-nouvelles-instances-de-france-galop/30208</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incertain</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>affinite_cheval</t>
+          <t>proprietaire_chevaux</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>mention équestre générique</t>
+          <t>haras</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5097,7 +5093,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5107,44 +5103,48 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Maurice Cohen</t>
+          <t>Nicolas Darribere</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Chef d'entreprise (transports T.M.C)</t>
+          <t>Cadre / dirigeant (jardinerie)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Transports T.M.C</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>Jardi Béarn</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Béarn (64)</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/maurice-cohen-4147a037</t>
+          <t>https://fr.linkedin.com/in/nicolas-darribere-733553178</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+          <t>Profil remonté 2x sur requêtes « équitation »/« cheval » + dirigeant</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « propriétaire » + « cheval de course » + dirigeant</t>
+          <t>Requêtes Google dirigeante/président + équitation/cheval</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/maurice-cohen-4147a037</t>
+          <t>https://fr.linkedin.com/in/nicolas-darribere-733553178</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5186,53 +5186,53 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B-profil LinkedIn à qualifier</t>
+          <t>B-à qualifier (presse)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alexis Mascheroni</t>
+          <t>Morgane Suquart</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cadre hôtellerie</t>
+          <t>Fondatrice</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grand Hôtel Cabourg - MGallery</t>
+          <t>MMProcess</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cabourg (14)</t>
+          <t>Saint-Pierre-Quiberon (56)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/alexis-mascheroni-217b86298</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Morgane%20Suquart%20MMProcess</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Événement équestre à l'hippodrome de Cabourg mentionné sur le profil</t>
+          <t>Contenu la montrant à cheval (snippet presse/LinkedIn)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Requête Google RH + équitation; participation à un événement à l'hippodrome de Cabourg</t>
+          <t>Fondatrice de la PME MMProcess, contenu la présentant à cheval</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/alexis-mascheroni-217b86298</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Morgane%20Suquart%20MMProcess</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5279,7 +5279,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5289,44 +5289,40 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gaëlle Baucheron</t>
+          <t>Julie André</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cadre</t>
+          <t>Front Office Manager (hôtellerie)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Caen (14)</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/ga%C3%ABlle-baucheron-1a4aaa145</t>
+          <t>https://fr.linkedin.com/in/julie-andre-b90a35157</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passionnée de chevaux »</t>
+          <t>Galop 7 d'équitation affiché sur le profil (diplôme 2010)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Requête Google "passionnée de chevaux" + directeur/responsable</t>
+          <t>Profil LinkedIn mentionnant le Galop 7 (requête site:linkedin "galop 7" + manager)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/ga%C3%ABlle-baucheron-1a4aaa145</t>
+          <t>https://fr.linkedin.com/in/julie-andre-b90a35157</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5351,7 +5347,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5368,7 +5364,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5378,69 +5374,69 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Zoé Jossart</t>
+          <t>Maurice Cohen</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chargée de missions événementielles</t>
+          <t>Chef d'entreprise (transports T.M.C)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Événementiel (équestre)</t>
+          <t>Transports T.M.C</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/zo%C3%A9-jossart</t>
+          <t>https://fr.linkedin.com/in/maurice-cohen-4147a037</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Profil remonté deux fois sur des requêtes équestres distinctes</t>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Requêtes Google "passionnée de chevaux" et "concours d'équitation"</t>
+          <t>Profil remonté sur requête « propriétaire » + « cheval de course » + dirigeant</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/zo%C3%A9-jossart</t>
+          <t>https://fr.linkedin.com/in/maurice-cohen-4147a037</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incertain</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>incertain</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>affinite_cheval</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>mention équestre générique</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5457,7 +5453,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5467,65 +5463,73 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fanny Avezac-Argelier</t>
+          <t>Alexis Mascheroni</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fondatrice et dirigeante</t>
+          <t>Cadre hôtellerie</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CAP'</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>Grand Hôtel Cabourg - MGallery</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Cabourg (14)</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/fanny-avezac-argelier-6b3965b8</t>
+          <t>https://fr.linkedin.com/in/alexis-mascheroni-217b86298</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + fondatrice/dirigeante</t>
+          <t>Événement équestre à l'hippodrome de Cabourg mentionné sur le profil</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Requête Google « cavalière » + fondatrice</t>
+          <t>Requête Google RH + équitation; participation à un événement à l'hippodrome de Cabourg</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/fanny-avezac-argelier-6b3965b8</t>
+          <t>https://fr.linkedin.com/in/alexis-mascheroni-217b86298</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>incertain</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>aucun</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5542,7 +5546,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5552,61 +5556,69 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Uranga</t>
+          <t>Gaëlle Baucheron</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cofondatrice et dirigeante</t>
+          <t>Cadre</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Caen (14)</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/franceuranga</t>
+          <t>https://fr.linkedin.com/in/ga%C3%ABlle-baucheron-1a4aaa145</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + dirigeante</t>
+          <t>Profil remonté sur requête « passionnée de chevaux »</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Requête Google « cavalière » + cofondatrice/dirigeante</t>
+          <t>Requête Google "passionnée de chevaux" + directeur/responsable</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/franceuranga</t>
+          <t>https://fr.linkedin.com/in/ga%C3%ABlle-baucheron-1a4aaa145</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>incertain</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>aucun</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5623,7 +5635,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5633,61 +5645,69 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Christine Caïn</t>
+          <t>Zoé Jossart</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dirigeante</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>Chargée de missions événementielles</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Événementiel (équestre)</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/christineca%C3%AFn/en</t>
+          <t>https://fr.linkedin.com/in/zo%C3%A9-jossart</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + dirigeante</t>
+          <t>Profil remonté deux fois sur des requêtes équestres distinctes</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Requête Google « cavalière » + dirigeante</t>
+          <t>Requêtes Google "passionnée de chevaux" et "concours d'équitation"</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/christineca%C3%AFn/en</t>
+          <t>https://fr.linkedin.com/in/zo%C3%A9-jossart</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>incertain</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>aucun</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>affinite_cheval</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>mention équestre générique</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5704,7 +5724,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5714,44 +5734,44 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valérie Sevestre</t>
+          <t>Fanny Avezac-Argelier</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Dirigeante / réseau d'affaires</t>
+          <t>Fondatrice et dirigeante</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BNI</t>
+          <t>CAP'</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/valerie-sevestre</t>
+          <t>https://fr.linkedin.com/in/fanny-avezac-argelier-6b3965b8</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + dirigeante</t>
+          <t>Profil remonté sur requête « cavalière » + fondatrice/dirigeante</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Requête Google « cavalière » + dirigeante</t>
+          <t>Requête Google « cavalière » + fondatrice</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/valerie-sevestre</t>
+          <t>https://fr.linkedin.com/in/fanny-avezac-argelier-6b3965b8</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5789,7 +5809,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5799,43 +5819,35 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Carole Juge-Llewellyn</t>
+          <t>France Uranga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CEO &amp; fondatrice</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>JOONE</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
+          <t>Cofondatrice et dirigeante</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/carolejuge</t>
+          <t>https://fr.linkedin.com/in/franceuranga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + CEO</t>
+          <t>Profil remonté sur requête « cavalière » + dirigeante</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Requête Google « cavalière » + CEO/fondatrice</t>
+          <t>Requête Google « cavalière » + cofondatrice/dirigeante</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/carolejuge</t>
+          <t>https://fr.linkedin.com/in/franceuranga</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5878,7 +5890,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5888,23 +5900,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Emilie Gallet</t>
+          <t>Christine Caïn</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Consultante (transformation &amp; organisation)</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Indépendante</t>
-        </is>
-      </c>
+          <t>Dirigeante</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/emilie-gallet-conseil</t>
+          <t>https://fr.linkedin.com/in/christineca%C3%AFn/en</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -5920,7 +5928,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/emilie-gallet-conseil</t>
+          <t>https://fr.linkedin.com/in/christineca%C3%AFn/en</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5963,7 +5971,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5973,19 +5981,23 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Juliette Borie</t>
+          <t>Valérie Sevestre</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Directeur Immobilier Groupe</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>Dirigeante / réseau d'affaires</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BNI</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/juliette-borie</t>
+          <t>https://fr.linkedin.com/in/valerie-sevestre</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -5996,17 +6008,17 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Requête Google « cavalière » + dirigeante/CEO</t>
+          <t>Requête Google « cavalière » + dirigeante</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/juliette-borie</t>
+          <t>https://fr.linkedin.com/in/valerie-sevestre</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6044,7 +6056,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6054,17 +6066,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Stéphane Baller</t>
+          <t>Carole Juge-Llewellyn</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Avocat / Of counsel (ex-associé)</t>
+          <t>CEO &amp; fondatrice</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>De Gaulle Fleurance &amp; Associés</t>
+          <t>JOONE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6074,28 +6086,28 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/stephane-baller-6858b93</t>
+          <t>https://fr.linkedin.com/in/carolejuge</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalier amateur » + « concours » + dirigeant</t>
+          <t>Profil remonté sur requête « cavalière » + CEO</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Requête Google « cavalier amateur » + concours + dirigeant</t>
+          <t>Requête Google « cavalière » + CEO/fondatrice</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/stephane-baller-6858b93</t>
+          <t>https://fr.linkedin.com/in/carolejuge</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6133,7 +6145,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6143,48 +6155,44 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Geoffroy Roux de Bézieux</t>
+          <t>Emilie Gallet</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Entrepreneur / investisseur / Président d'honneur du MEDEF</t>
+          <t>Consultante (transformation &amp; organisation)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Notus Technologies</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
+          <t>Indépendante</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/geoffroy-roux-de-bezieux</t>
+          <t>https://fr.linkedin.com/in/emilie-gallet-conseil</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalier amateur » + « concours »; signal incertain</t>
+          <t>Profil remonté sur requête « cavalière » + dirigeante</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Requête Google « cavalier amateur » + concours + dirigeant; à vérifier (possible faux positif)</t>
+          <t>Requête Google « cavalière » + dirigeante</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/geoffroy-roux-de-bezieux</t>
+          <t>https://fr.linkedin.com/in/emilie-gallet-conseil</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6222,7 +6230,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6232,40 +6240,40 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Raphaëlle Coquibus</t>
+          <t>Juliette Borie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RH / DRH / dirigeante</t>
+          <t>Directeur Immobilier Groupe</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Raphaelle%20Coquibus</t>
+          <t>https://fr.linkedin.com/in/juliette-borie</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Post LinkedIn sur l'accompagnement « autrement » (leadership/posture)</t>
+          <t>Profil remonté sur requête « cavalière » + dirigeante</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Post LinkedIn remonté sur requête cavalière + leadership + DRH</t>
+          <t>Requête Google « cavalière » + dirigeante/CEO</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/posts/%F0%9F%8E%A4-raphaelle-coquibus-%F0%9F%90%BE-03244a42_accompagnementautrement-leadership-posture-activity-7338448673242013696-pYfo</t>
+          <t>https://fr.linkedin.com/in/juliette-borie</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6303,27 +6311,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B-à qualifier (presse)</t>
+          <t>B-profil LinkedIn à qualifier</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jacques-Henri Eyraud</t>
+          <t>Stéphane Baller</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Dirigeant / investisseur (ex-président OM)</t>
+          <t>Avocat / Of counsel (ex-associé)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Turf Éditions / Paris-Turf (repreneur 2013)</t>
+          <t>De Gaulle Fleurance &amp; Associés</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6333,28 +6341,28 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Jacques-Henri%20Eyraud</t>
+          <t>https://fr.linkedin.com/in/stephane-baller-6858b93</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>A investi dans la presse hippique (Turf Éditions); affinité courses à confirmer</t>
+          <t>Profil remonté sur requête « cavalier amateur » + « concours » + dirigeant</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Repreneur du groupe Paris-Turf en 2013 (66%)</t>
+          <t>Requête Google « cavalier amateur » + concours + dirigeant</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://fr.wikipedia.org/wiki/Turf_%C3%89ditions</t>
+          <t>https://fr.linkedin.com/in/stephane-baller-6858b93</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6392,58 +6400,58 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A-presse</t>
+          <t>B-profil LinkedIn à qualifier</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Manuel Demnard</t>
+          <t>Geoffroy Roux de Bézieux</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ex-chef d'entreprise; président de l'association des courses de Toulouse</t>
+          <t>Entrepreneur / investisseur / Président d'honneur du MEDEF</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Association sportive des courses de Toulouse (La Cépière)</t>
+          <t>Notus Technologies</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Toulouse (31)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Manuel%20Demnard</t>
+          <t>https://fr.linkedin.com/in/geoffroy-roux-de-bezieux</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Ancien chef d'entreprise devenu président d'hippodrome (500 K EUR investis)</t>
+          <t>Profil remonté sur requête « cavalier amateur » + « concours »; signal incertain</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Élu président en juin 2023, ancien chef d'entreprise (Gazette du Midi)</t>
+          <t>Requête Google « cavalier amateur » + concours + dirigeant; à vérifier (possible faux positif)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://gazette-du-midi.fr/au-sommaire/entreprises/l-hippodrome-de-toulouse-la-cepiere</t>
+          <t>https://fr.linkedin.com/in/geoffroy-roux-de-bezieux</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6481,7 +6489,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6491,44 +6499,40 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alexis Perrin</t>
+          <t>Raphaëlle Coquibus</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Consultant / associé</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Abelya Partners</t>
-        </is>
-      </c>
+          <t>RH / DRH / dirigeante</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/perrinalexis/en</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Raphaelle%20Coquibus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « galop 7 » + fondateur/manager</t>
+          <t>Post LinkedIn sur l'accompagnement « autrement » (leadership/posture)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Requête Google site:linkedin "galop 7"; indice à confirmer</t>
+          <t>Post LinkedIn remonté sur requête cavalière + leadership + DRH</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/perrinalexis/en</t>
+          <t>https://fr.linkedin.com/posts/%F0%9F%8E%A4-raphaelle-coquibus-%F0%9F%90%BE-03244a42_accompagnementautrement-leadership-posture-activity-7338448673242013696-pYfo</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6566,54 +6570,58 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B-profil LinkedIn à qualifier</t>
+          <t>B-à qualifier (presse)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Narimane Langlois</t>
+          <t>Jacques-Henri Eyraud</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fondatrice</t>
+          <t>Dirigeant / investisseur (ex-président OM)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MANAM Design</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>Turf Éditions / Paris-Turf (repreneur 2013)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/narimane-langlois</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Jacques-Henri%20Eyraud</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passion équestre » + fondatrice</t>
+          <t>A investi dans la presse hippique (Turf Éditions); affinité courses à confirmer</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Requête Google "passion équestre"/"sports équestres" + fondatrice</t>
+          <t>Repreneur du groupe Paris-Turf en 2013 (66%)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/narimane-langlois</t>
+          <t>https://fr.wikipedia.org/wiki/Turf_%C3%89ditions</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6651,54 +6659,58 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B-profil LinkedIn à qualifier</t>
+          <t>A-presse</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Émilie Prudence</t>
+          <t>Manuel Demnard</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Dirigeante</t>
+          <t>Ex-chef d'entreprise; président de l'association des courses de Toulouse</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Phoenix Evènements</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>Association sportive des courses de Toulouse (La Cépière)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/%C3%A9milie-prudence-phoenix</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Manuel%20Demnard</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passion équestre » + dirigeante</t>
+          <t>Ancien chef d'entreprise devenu président d'hippodrome (500 K EUR investis)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Requête Google "passion équestre" + dirigeante</t>
+          <t>Élu président en juin 2023, ancien chef d'entreprise (Gazette du Midi)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/%C3%A9milie-prudence-phoenix</t>
+          <t>https://gazette-du-midi.fr/au-sommaire/entreprises/l-hippodrome-de-toulouse-la-cepiere</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>75</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6736,7 +6748,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6746,44 +6758,44 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cindy Girerd</t>
+          <t>Alexis Perrin</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Fondatrice</t>
+          <t>Consultant / associé</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Com' Killer</t>
+          <t>Abelya Partners</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/cindy-girerd</t>
+          <t>https://fr.linkedin.com/in/perrinalexis/en</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passion équestre » + fondatrice (événementiel sportif)</t>
+          <t>Profil remonté sur requête « galop 7 » + fondateur/manager</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Requête Google "passion équestre" + fondatrice</t>
+          <t>Requête Google site:linkedin "galop 7"; indice à confirmer</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/cindy-girerd</t>
+          <t>https://fr.linkedin.com/in/perrinalexis/en</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6821,7 +6833,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6831,40 +6843,44 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Emmeline Lambard</t>
+          <t>Narimane Langlois</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fondatrice - Dirigeante</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>Fondatrice</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>MANAM Design</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/emmeline-lambard-14018a273</t>
+          <t>https://fr.linkedin.com/in/narimane-langlois</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passion équestre » + fondatrice/dirigeante</t>
+          <t>Profil remonté sur requête « passion équestre » + fondatrice</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Requête Google "passion équestre" + dirigeante</t>
+          <t>Requête Google "passion équestre"/"sports équestres" + fondatrice</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/emmeline-lambard-14018a273</t>
+          <t>https://fr.linkedin.com/in/narimane-langlois</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6902,7 +6918,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6912,48 +6928,44 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>François Singer</t>
+          <t>Émilie Prudence</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Directeur Général</t>
+          <t>Dirigeante</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sportmed Summit / sport business</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
+          <t>Phoenix Evènements</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/fran%C3%A7ois-singer-8b06722b</t>
+          <t>https://fr.linkedin.com/in/%C3%A9milie-prudence-phoenix</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « sports équestres » + directeur</t>
+          <t>Profil remonté sur requête « passion équestre » + dirigeante</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Requête Google "sports équestres" + directeur</t>
+          <t>Requête Google "passion équestre" + dirigeante</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/fran%C3%A7ois-singer-8b06722b</t>
+          <t>https://fr.linkedin.com/in/%C3%A9milie-prudence-phoenix</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6991,7 +7003,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7001,48 +7013,44 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lucile Sachot</t>
+          <t>Cindy Girerd</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cadre</t>
+          <t>Fondatrice</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chambre d'Agriculture de la Lozère</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Lozère</t>
-        </is>
-      </c>
+          <t>Com' Killer</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/lucile-sachot-128a31178</t>
+          <t>https://fr.linkedin.com/in/cindy-girerd</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « passion équestre » + responsable</t>
+          <t>Profil remonté sur requête « passion équestre » + fondatrice (événementiel sportif)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Requête Google "passion équestre" + responsable</t>
+          <t>Requête Google "passion équestre" + fondatrice</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/lucile-sachot-128a31178</t>
+          <t>https://fr.linkedin.com/in/cindy-girerd</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7080,54 +7088,50 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A-presse</t>
+          <t>B-profil LinkedIn à qualifier</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Guy d'Arexy</t>
+          <t>Emmeline Lambard</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fondateur</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Agence Globale</t>
-        </is>
-      </c>
+          <t>Fondatrice - Dirigeante</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Guy%20d'Arexy</t>
+          <t>https://fr.linkedin.com/in/emmeline-lambard-14018a273</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Ex-gentleman-rider, fondateur de l'Agence Globale, membre du bureau du Club GRC</t>
+          <t>Profil remonté sur requête « passion équestre » + fondatrice/dirigeante</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Nouveau membre du bureau : ancien gentleman-rider et fondateur de l'Agence Globale (Jour de Galop)</t>
+          <t>Requête Google "passion équestre" + dirigeante</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.jourdegalop.com/2023/05/le-club-des-gentlemen-demenage-et-elit-son-bureau/</t>
+          <t>https://fr.linkedin.com/in/emmeline-lambard-14018a273</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7165,54 +7169,58 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A-presse</t>
+          <t>B-profil LinkedIn à qualifier</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Georges-Alexandre Ancenys</t>
+          <t>François Singer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Dirigeant du fonds d'investissement SPE Capital</t>
+          <t>Directeur Général</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SPE Capital</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>Sportmed Summit / sport business</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/people/?keywords=Georges-Alexandre%20Ancenys</t>
+          <t>https://fr.linkedin.com/in/fran%C3%A7ois-singer-8b06722b</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Membre du bureau du Club des Gentlemen-Riders (cavalier de courses amateur)</t>
+          <t>Profil remonté sur requête « sports équestres » + directeur</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Nouveau membre du bureau : à la tête du fonds d'investissement SPE Capital (Jour de Galop)</t>
+          <t>Requête Google "sports équestres" + directeur</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.jourdegalop.com/2023/05/le-club-des-gentlemen-demenage-et-elit-son-bureau/</t>
+          <t>https://fr.linkedin.com/in/fran%C3%A7ois-singer-8b06722b</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7250,7 +7258,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7260,40 +7268,48 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>François de Rouffignac</t>
+          <t>Lucile Sachot</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DRH (hôtellerie-restauration)</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+          <t>Cadre</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Chambre d'Agriculture de la Lozère</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lozère</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/fran%C3%A7ois-de-rouffignac-53832427</t>
+          <t>https://fr.linkedin.com/in/lucile-sachot-128a31178</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+          <t>Profil remonté sur requête « passion équestre » + responsable</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière/cavalier » + ressources humaines</t>
+          <t>Requête Google "passion équestre" + responsable</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/fran%C3%A7ois-de-rouffignac-53832427</t>
+          <t>https://fr.linkedin.com/in/lucile-sachot-128a31178</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7331,54 +7347,54 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B-profil LinkedIn à qualifier</t>
+          <t>A-presse</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lou Froissardey</t>
+          <t>Guy d'Arexy</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Chargée des Ressources Humaines</t>
+          <t>Fondateur</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ECM Besançon</t>
+          <t>Agence Globale</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/lou-froissardey-754937221</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Guy%20d'Arexy</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+          <t>Ex-gentleman-rider, fondateur de l'Agence Globale, membre du bureau du Club GRC</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + ressources humaines</t>
+          <t>Nouveau membre du bureau : ancien gentleman-rider et fondateur de l'Agence Globale (Jour de Galop)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/lou-froissardey-754937221</t>
+          <t>https://www.jourdegalop.com/2023/05/le-club-des-gentlemen-demenage-et-elit-son-bureau/</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>80</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7416,54 +7432,54 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B-profil LinkedIn à qualifier</t>
+          <t>A-presse</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Élodie Dehen</t>
+          <t>Georges-Alexandre Ancenys</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cadre</t>
+          <t>Dirigeant du fonds d'investissement SPE Capital</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ARESCOM (informatique)</t>
+          <t>SPE Capital</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/elodie-dehen-252a72188</t>
+          <t>https://www.linkedin.com/search/results/people/?keywords=Georges-Alexandre%20Ancenys</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+          <t>Membre du bureau du Club des Gentlemen-Riders (cavalier de courses amateur)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + recrutement</t>
+          <t>Nouveau membre du bureau : à la tête du fonds d'investissement SPE Capital (Jour de Galop)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/elodie-dehen-252a72188</t>
+          <t>https://www.jourdegalop.com/2023/05/le-club-des-gentlemen-demenage-et-elit-son-bureau/</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7501,7 +7517,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7511,23 +7527,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chantal Laterrade</t>
+          <t>François de Rouffignac</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Chargée de recrutement</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>FMS Entreprise Adaptée</t>
-        </is>
-      </c>
+          <t>DRH (hôtellerie-restauration)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/chantal-laterrade-a4b12821b</t>
+          <t>https://fr.linkedin.com/in/fran%C3%A7ois-de-rouffignac-53832427</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -7538,17 +7550,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + recrutement</t>
+          <t>Profil remonté sur requête « cavalière/cavalier » + ressources humaines</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/chantal-laterrade-a4b12821b</t>
+          <t>https://fr.linkedin.com/in/fran%C3%A7ois-de-rouffignac-53832427</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7586,7 +7598,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7596,44 +7608,44 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gérald Brault</t>
+          <t>Lou Froissardey</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Dirigeant (distributeur de produits équins)</t>
+          <t>Chargée des Ressources Humaines</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Distribution équine (TPE)</t>
+          <t>ECM Besançon</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/g%C3%A9rald-brault-07161a97</t>
+          <t>https://fr.linkedin.com/in/lou-froissardey-754937221</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Cavalier pratiquant affiché sur le profil (dirigeant de TPE)</t>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Profil « Cavalier, distributeur de produits equins » — cavalier pratiquant (NB: déjà dans la filière équine)</t>
+          <t>Profil remonté sur requête « cavalière » + ressources humaines</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/g%C3%A9rald-brault-07161a97</t>
+          <t>https://fr.linkedin.com/in/lou-froissardey-754937221</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>35</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7671,7 +7683,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7681,23 +7693,23 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lamia Moraine</t>
+          <t>Élodie Dehen</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cofondatrice &amp; Directrice Générale</t>
+          <t>Cadre</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Inovelite</t>
+          <t>ARESCOM (informatique)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/lamia-moraine-inovelite</t>
+          <t>https://fr.linkedin.com/in/elodie-dehen-252a72188</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -7708,17 +7720,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + cofondatrice/DG (PME)</t>
+          <t>Profil remonté sur requête « cavalière » + recrutement</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/lamia-moraine-inovelite</t>
+          <t>https://fr.linkedin.com/in/elodie-dehen-252a72188</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7756,7 +7768,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7766,23 +7778,23 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Isabelle Delannoy</t>
+          <t>Chantal Laterrade</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Présidente</t>
+          <t>Chargée de recrutement</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>L'Entreprise Symbiotique</t>
+          <t>FMS Entreprise Adaptée</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/isabelle-delannoy-8337225</t>
+          <t>https://fr.linkedin.com/in/chantal-laterrade-a4b12821b</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -7793,17 +7805,17 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + présidente (petite structure)</t>
+          <t>Profil remonté sur requête « cavalière » + recrutement</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/isabelle-delannoy-8337225</t>
+          <t>https://fr.linkedin.com/in/chantal-laterrade-a4b12821b</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7841,7 +7853,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7851,44 +7863,44 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eve Pauvert</t>
+          <t>Gérald Brault</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Dirigeante</t>
+          <t>Dirigeant (distributeur de produits équins)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Facilis.fr (TPE/PME, Alsace)</t>
+          <t>Distribution équine (TPE)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/eve-pauvert-dirigeante-facilis-cse-tpe-pme-alsace-grandest</t>
+          <t>https://fr.linkedin.com/in/g%C3%A9rald-brault-07161a97</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+          <t>Cavalier pratiquant affiché sur le profil (dirigeant de TPE)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « dirigeante » TPE/PME + « cavalière »/concours</t>
+          <t>Profil « Cavalier, distributeur de produits equins » — cavalier pratiquant (NB: déjà dans la filière équine)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/eve-pauvert-dirigeante-facilis-cse-tpe-pme-alsace-grandest</t>
+          <t>https://fr.linkedin.com/in/g%C3%A9rald-brault-07161a97</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7926,7 +7938,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7936,23 +7948,23 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vanessa Logerais</t>
+          <t>Lamia Moraine</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Fondatrice / dirigeante</t>
+          <t>Cofondatrice &amp; Directrice Générale</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Parangone (agence)</t>
+          <t>Inovelite</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/vanessa-logerais-parangone</t>
+          <t>https://fr.linkedin.com/in/lamia-moraine-inovelite</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -7963,12 +7975,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « dirigeante » PME + « cavalière »</t>
+          <t>Profil remonté sur requête « cavalière » + cofondatrice/DG (PME)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/vanessa-logerais-parangone</t>
+          <t>https://fr.linkedin.com/in/lamia-moraine-inovelite</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8011,7 +8023,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8021,7 +8033,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rafaëlle Rivier</t>
+          <t>Isabelle Delannoy</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8031,13 +8043,13 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MOMA Consulting</t>
+          <t>L'Entreprise Symbiotique</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/rafaelle-rivier</t>
+          <t>https://fr.linkedin.com/in/isabelle-delannoy-8337225</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -8048,12 +8060,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « dirigeante » + « cavalière »/concours (conseil, PME)</t>
+          <t>Profil remonté sur requête « cavalière » + présidente (petite structure)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/rafaelle-rivier</t>
+          <t>https://fr.linkedin.com/in/isabelle-delannoy-8337225</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8096,7 +8108,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>224</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8106,23 +8118,23 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pauline Laigneau</t>
+          <t>Eve Pauvert</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Fondatrice</t>
+          <t>Dirigeante</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gemmyo / Demian Education</t>
+          <t>Facilis.fr (TPE/PME, Alsace)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/pauline-laigneau</t>
+          <t>https://fr.linkedin.com/in/eve-pauvert-dirigeante-facilis-cse-tpe-pme-alsace-grandest</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -8133,17 +8145,17 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Profil remonté sur requête « cavalière » + fondatrice (à confirmer; taille Gemmyo à vérifier)</t>
+          <t>Profil remonté sur requête « dirigeante » TPE/PME + « cavalière »/concours</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/pauline-laigneau</t>
+          <t>https://fr.linkedin.com/in/eve-pauvert-dirigeante-facilis-cse-tpe-pme-alsace-grandest</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>45</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8181,7 +8193,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8191,44 +8203,44 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Caroline Clavel</t>
+          <t>Vanessa Logerais</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Gérante</t>
+          <t>Fondatrice / dirigeante</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Écurie (TPE)</t>
+          <t>Parangone (agence)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/caroline-clavel-40ba79197</t>
+          <t>https://fr.linkedin.com/in/vanessa-logerais-parangone</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Cavalière pratiquante affichée sur le profil (gérante de TPE)</t>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Profil « Gérante - Cavalière » — cavalière pratiquante (NB: gère une écurie, filière équine)</t>
+          <t>Profil remonté sur requête « dirigeante » PME + « cavalière »</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/in/caroline-clavel-40ba79197</t>
+          <t>https://fr.linkedin.com/in/vanessa-logerais-parangone</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8258,6 +8270,261 @@
         </is>
       </c>
       <c r="S89" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Rafaëlle Rivier</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Présidente</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>MOMA Consulting</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/rafaelle-rivier</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « dirigeante » + « cavalière »/concours (conseil, PME)</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/rafaelle-rivier</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Pauline Laigneau</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fondatrice</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Gemmyo / Demian Education</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/pauline-laigneau</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Indice équestre détecté via requête Google croisée (à confirmer sur le profil)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Profil remonté sur requête « cavalière » + fondatrice (à confirmer; taille Gemmyo à vérifier)</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/pauline-laigneau</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>B-profil LinkedIn à qualifier</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Caroline Clavel</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Gérante</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Écurie (TPE)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/caroline-clavel-40ba79197</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Cavalière pratiquante affichée sur le profil (gérante de TPE)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Profil « Gérante - Cavalière » — cavalière pratiquante (NB: gère une écurie, filière équine)</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/in/caroline-clavel-40ba79197</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>TPE/PME estimée (&lt;100)</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
